--- a/food_beverage_order_forms/039_gluten_free_meal_subscription_signup--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/039_gluten_free_meal_subscription_signup--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2083,352 +2083,352 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>american_samoa</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>district_of_columbia</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>puerto_rico</t>
+          <t>pay_pal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Pay Pal</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>u.s._virgin_islands</t>
+          <t>apple_pay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>U.S. Virgin Islands</t>
+          <t>Apple Pay</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>guam</t>
+          <t>google_pay</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Google Pay</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>american_samoa</t>
+          <t>amazon_pay</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Amazon Pay</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>northern_mariana_islands</t>
+          <t>venmo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Mariana Islands</t>
+          <t>Venmo</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>delivery_state_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>district_of_columbia</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>credit_card</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pay_pal</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pay Pal</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>apple_pay</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Apple Pay</t>
+          <t>Every 2 Weeks</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>google_pay</t>
+          <t>every_4_weeks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Google Pay</t>
+          <t>Every 4 Weeks</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>gluten_free_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>amazon_pay</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Amazon Pay</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>gluten_free_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>venmo</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Venmo</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>every_3_days</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Every 3 Days</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>payment_frequency_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>every_4_days</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Every 4 Days</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>payment_frequency_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Every Week</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>payment_frequency_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>every_10_days</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Every 2 Weeks</t>
+          <t>Every 10 Days</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>payment_frequency_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>every_4_weeks</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Every 4 Weeks</t>
+          <t>Every 2 Weeks</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gluten_free_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>every_3_weeks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Every 3 Weeks</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gluten_free_choices</t>
+          <t>delivery_frequency_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>every_4_weeks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Every 4 Weeks</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>every_3_days</t>
+          <t>every_2_months</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Every 3 Days</t>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>every_4_days</t>
+          <t>every_3_months</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Every 4 Days</t>
+          <t>Every 3 Months</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>every_week</t>
+          <t>every_4_months</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Every Week</t>
+          <t>Every 4 Months</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>every_10_days</t>
+          <t>every_6_months</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Every 10 Days</t>
+          <t>Every 6 Months</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>every_8_months</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Every 2 Weeks</t>
+          <t>Every 8 Months</t>
         </is>
       </c>
     </row>
@@ -2525,257 +2525,257 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>every_3_weeks</t>
+          <t>every_12_months</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Every 3 Weeks</t>
+          <t>Every 12 Months</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>every_4_weeks</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Every 4 Weeks</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>every_2_months</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Every 2 Months</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>every_3_months</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Every 3 Months</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>every_4_months</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Every 4 Months</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>every_6_months</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Every 6 Months</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>every_8_months</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Every 8 Months</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_day_of_week_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>every_12_months</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Every 12 Months</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>pay_pal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Pay Pal</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>apple_pay</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Apple Pay</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>google_pay</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Google Pay</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>amazon_pay</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Amazon Pay</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>venmo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Venmo</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>delivery_day_of_week_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2809,7 +2809,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2826,7 +2826,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>payment_method_2_choices</t>
+          <t>payment_method_3_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2894,7 +2894,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>payment_method_3_choices</t>
+          <t>payment_method_4_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>payment_method_4_choices</t>
+          <t>payment_method_5_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3132,321 +3132,202 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>credit_card</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>pay_pal</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pay Pal</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>apple_pay</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Apple Pay</t>
+          <t>Every 2 Weeks</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>google_pay</t>
+          <t>every_4_weeks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Google Pay</t>
+          <t>Every 4 Weeks</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_3_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>amazon_pay</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Amazon Pay</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_3_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>venmo</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Venmo</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>payment_method_5_choices</t>
+          <t>payment_frequency_3_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Every 2 Weeks</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>payment_frequency_2_choices</t>
+          <t>payment_frequency_3_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>every_4_weeks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Every 4 Weeks</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>payment_frequency_2_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>payment_frequency_2_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Every 2 Weeks</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>payment_frequency_2_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>every_4_weeks</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Every 4 Weeks</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>payment_frequency_3_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>payment_frequency_3_choices</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>payment_frequency_3_choices</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>every_2_weeks</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Every 2 Weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>payment_frequency_3_choices</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>every_4_weeks</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Every 4 Weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
